--- a/listini-c75s/PF1_SENZA_VETRO.xlsx
+++ b/listini-c75s/PF1_SENZA_VETRO.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Parametri" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Coefficienti" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Ferramenta" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="FerrGriglia" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -514,35 +515,35 @@
         <v>1900</v>
       </c>
       <c r="B3" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B2+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C3" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C2+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D3" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D2+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E3" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E2+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F3" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F2+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G3" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G2+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H3" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H2+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I3" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A3)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A3)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A3)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I2+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -551,35 +552,35 @@
         <v>2000</v>
       </c>
       <c r="B4" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B3+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C4" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C3+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D4" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D3+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E4" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E3+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F4" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F3+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G4" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G3+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H4" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H3+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I4" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A4)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A4)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A4)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I3+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -588,35 +589,35 @@
         <v>2100</v>
       </c>
       <c r="B5" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B4+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C5" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C4+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D5" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D4+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E5" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E4+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F5" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F4+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G5" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G4+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H5" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H4+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I5" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A5)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A5)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A5)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I4+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -625,35 +626,35 @@
         <v>2200</v>
       </c>
       <c r="B6" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B5+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C6" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C5+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D6" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D5+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E6" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E5+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F6" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F5+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G6" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G5+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H6" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H5+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I6" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A6)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A6)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A6)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I5+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -662,35 +663,35 @@
         <v>2300</v>
       </c>
       <c r="B7" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B6+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C7" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C6+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D7" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D6+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E7" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E6+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F7" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F6+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G7" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G6+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H7" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H6+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I7" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A7)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A7)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A7)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I6+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -699,35 +700,35 @@
         <v>2400</v>
       </c>
       <c r="B8" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B7+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C8" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C7+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D8" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D7+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E8" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E7+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F8" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F7+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G8" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G7+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H8" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H7+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I8" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A8)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A8)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A8)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I7+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -736,35 +737,35 @@
         <v>2500</v>
       </c>
       <c r="B9" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B8+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C9" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C8+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D9" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D8+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E9" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E8+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F9" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F8+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G9" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G8+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H9" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H8+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I9" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A9)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A9)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A9)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I8+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -773,35 +774,35 @@
         <v>2600</v>
       </c>
       <c r="B10" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B9+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C10" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C9+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D10" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D9+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E10" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E9+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F10" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F9+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G10" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G9+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H10" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H9+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I10" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A10)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A10)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A10)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I9+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -810,35 +811,35 @@
         <v>2700</v>
       </c>
       <c r="B11" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B10+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="C11" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C10+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="D11" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D10+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="E11" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E10+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="F11" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F10+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="G11" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G10+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="H11" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H10+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
       <c r="I11" s="4">
-        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
+        <f>ROUND(ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$2+Coefficienti!$B$3*$A11)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$2+Coefficienti!$B$6*$A11)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$2+Coefficienti!$B$9*$A11)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I10+Coefficienti!$B$11*Parametri!$B$6,2)*(1+Parametri!$B$7),2)</f>
         <v/>
       </c>
     </row>
@@ -885,35 +886,35 @@
         <v>1900</v>
       </c>
       <c r="B16" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B2+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C16" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C2+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D16" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D2+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E16" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E2+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F16" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F2+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G16" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G2+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H16" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H2+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I16" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A16)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A16)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A16)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I2+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -922,35 +923,35 @@
         <v>2000</v>
       </c>
       <c r="B17" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B3+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C17" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C3+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D17" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D3+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E17" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E3+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F17" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F3+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G17" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G3+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H17" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H3+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I17" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A17)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A17)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A17)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I3+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -959,35 +960,35 @@
         <v>2100</v>
       </c>
       <c r="B18" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B4+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C18" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C4+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D18" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D4+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E18" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E4+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F18" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F4+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G18" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G4+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H18" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H4+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I18" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A18)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A18)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A18)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I4+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -996,35 +997,35 @@
         <v>2200</v>
       </c>
       <c r="B19" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B5+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C19" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C5+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D19" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D5+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E19" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E5+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F19" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F5+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G19" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G5+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H19" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H5+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I19" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A19)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A19)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A19)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I5+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1033,35 +1034,35 @@
         <v>2300</v>
       </c>
       <c r="B20" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B6+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C20" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C6+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D20" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D6+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E20" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E6+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F20" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F6+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G20" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G6+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H20" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H6+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I20" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A20)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A20)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A20)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I6+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1070,35 +1071,35 @@
         <v>2400</v>
       </c>
       <c r="B21" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B7+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C21" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C7+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D21" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D7+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E21" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E7+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F21" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F7+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G21" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G7+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H21" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H7+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I21" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A21)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A21)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A21)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I7+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1107,35 +1108,35 @@
         <v>2500</v>
       </c>
       <c r="B22" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B8+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C22" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C8+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D22" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D8+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E22" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E8+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F22" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F8+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G22" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G8+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H22" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H8+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I22" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A22)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A22)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A22)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I8+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1144,35 +1145,35 @@
         <v>2600</v>
       </c>
       <c r="B23" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B9+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C23" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C9+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D23" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D9+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E23" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E9+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F23" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F9+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G23" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G9+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H23" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H9+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I23" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A23)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A23)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A23)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I9+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1181,35 +1182,35 @@
         <v>2700</v>
       </c>
       <c r="B24" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*B$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*B$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*B$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!B10+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="C24" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*C$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*C$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*C$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!C10+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="D24" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*D$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*D$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*D$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!D10+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="E24" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*E$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*E$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*E$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!E10+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="F24" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*F$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*F$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*F$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!F10+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="G24" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*G$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*G$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*G$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!G10+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="H24" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*H$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*H$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*H$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!H10+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
       <c r="I24" s="4">
-        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+Ferramenta!$D$11+Coefficienti!$B$11*Parametri!$B$6,2)</f>
+        <f>ROUND((((Coefficienti!$B$1+Coefficienti!$B$2*I$15+Coefficienti!$B$3*$A24)*Parametri!$B$1+(Coefficienti!$B$4+Coefficienti!$B$5*I$15+Coefficienti!$B$6*$A24)*Parametri!$B$2)*(1-Parametri!$B$3)+((Coefficienti!$B$7+Coefficienti!$B$8*I$15+Coefficienti!$B$9*$A24)+Coefficienti!$B$10)*(1-Parametri!$B$4))*(1+Parametri!$B$5)+FerrGriglia!I10+Coefficienti!$B$11*Parametri!$B$6,2)</f>
         <v/>
       </c>
     </row>
@@ -1502,7 +1503,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -1535,18 +1536,23 @@
           <t>Fonte</t>
         </is>
       </c>
+      <c r="G1" s="5" t="inlineStr">
+        <is>
+          <t>Kit Maico per la misura di riferimento 1000x1900 (FFB/FFH = anta-20). Le griglie usano il foglio FerrGriglia (kit per ogni misura).</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>Martellina DK (1033) — non nel netto 2025</t>
+          <t>Cremonese Multi-Matic (lvMWEspagnoletteGesamt) (201740)</t>
         </is>
       </c>
       <c r="B2" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <v>5.5</v>
+        <v>4.46</v>
       </c>
       <c r="D2" s="4">
         <f>B2*C2</f>
@@ -1554,21 +1560,21 @@
       </c>
       <c r="E2" s="5" t="inlineStr">
         <is>
-          <t>manuale</t>
+          <t>netto 2025</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
         <is>
-          <t>Cremonese Multi Matic GR1590 (201745)</t>
+          <t>Prolunga cremonese sopra (VerlaengerungFixOben) (201841)</t>
         </is>
       </c>
       <c r="B3" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="6" t="n">
-        <v>3.57</v>
+        <v>1.69</v>
       </c>
       <c r="D3" s="4">
         <f>B3*C3</f>
@@ -1583,14 +1589,14 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>Chiusura centrale MM (201752)</t>
+          <t>Prolunga cremonese sotto (VerlaengerungFixUnten) (201750)</t>
         </is>
       </c>
       <c r="B4" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>1.26</v>
+        <v>2.17</v>
       </c>
       <c r="D4" s="4">
         <f>B4*C4</f>
@@ -1605,7 +1611,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>Movimento angolare MM (222201)</t>
+          <t>Movimento angolare MM (Eckumlenkung) (222201)</t>
         </is>
       </c>
       <c r="B5" s="8" t="n">
@@ -1627,7 +1633,7 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Movimento angolare prolungabile (222209)</t>
+          <t>Movimento angolare verticale (EckumlenkungVertikal) (222209)</t>
         </is>
       </c>
       <c r="B6" s="8" t="n">
@@ -1649,14 +1655,14 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Scontro fungo scost.9 (356361)</t>
+          <t>Chiusura centrale lato cerniere (MittelverschlussEinteiligIS) (211931)</t>
         </is>
       </c>
       <c r="B7" s="8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>0.3728</v>
+        <v>2.66</v>
       </c>
       <c r="D7" s="4">
         <f>B7*C7</f>
@@ -1671,14 +1677,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Scontro nottolino (355866) — NON a listino</t>
+          <t>Chiusura centrale orizzontale (Mittelverschluss) (211929)</t>
         </is>
       </c>
       <c r="B8" s="8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="D8" s="4">
         <f>B8*C8</f>
@@ -1686,21 +1692,21 @@
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
-          <t>da inserire</t>
+          <t>netto 2025</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cerniere a vista (set anta) — DA INSERIRE</t>
+          <t>Forbice + braccio (ScherenMontiert) (211900)</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="D9" s="4">
         <f>B9*C9</f>
@@ -1708,21 +1714,21 @@
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>da inserire</t>
+          <t>netto 2025</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Forbice a vista + braccio — DA INSERIRE</t>
+          <t>Forbice + braccio (ScherenMontiert) (211901)</t>
         </is>
       </c>
       <c r="B10" s="8" t="n">
         <v>1</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="D10" s="4">
         <f>B10*C10</f>
@@ -1730,25 +1736,470 @@
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
-          <t>da inserire</t>
+          <t>netto 2025</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>TOTALE FERRAMENTA</t>
-        </is>
-      </c>
-      <c r="D11" s="10">
-        <f>SUM(D2:D10)</f>
-        <v/>
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Asta lato cerniere tagliabile (Drehbandstulp) (202269)</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="D11" s="4">
+        <f>B11*C11</f>
+        <v/>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>netto 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Cerniera angolare (ArtNrEcklager) (250400)</t>
+        </is>
+      </c>
+      <c r="B12" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="D12" s="4">
+        <f>B12*C12</f>
+        <v/>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>netto 2025</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
         <is>
+          <t>Bandella cerniera angolare (ArtNrEcklagerband) (215806)</t>
+        </is>
+      </c>
+      <c r="B13" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D13" s="4">
+        <f>B13*C13</f>
+        <v/>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>netto 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Scontro fungo IS (SchliessteilIS) (356361)</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>0.3728</v>
+      </c>
+      <c r="D14" s="4">
+        <f>B14*C14</f>
+        <v/>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>netto 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Martellina DK — non nel netto 2025 (1033)</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D15" s="4">
+        <f>B15*C15</f>
+        <v/>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>manuale</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Scontro nottolino personalizzato (VZPersonalisiert) — NON a listino (355866)</t>
+        </is>
+      </c>
+      <c r="B16" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4">
+        <f>B16*C16</f>
+        <v/>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
+        <is>
+          <t>da inserire</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>TOTALE FERRAMENTA</t>
+        </is>
+      </c>
+      <c r="D17" s="10">
+        <f>SUM(D2:D16)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
           <t>Celle gialle modificabili. Prezzi a 0 = da inserire: il listino li ignora finché vuoti.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="9" t="inlineStr">
+        <is>
+          <t>H/L</t>
+        </is>
+      </c>
+      <c r="B1" s="9" t="n">
+        <v>500</v>
+      </c>
+      <c r="C1" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="D1" s="9" t="n">
+        <v>700</v>
+      </c>
+      <c r="E1" s="9" t="n">
+        <v>800</v>
+      </c>
+      <c r="F1" s="9" t="n">
+        <v>900</v>
+      </c>
+      <c r="G1" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="H1" s="9" t="n">
+        <v>1100</v>
+      </c>
+      <c r="I1" s="9" t="n">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="9" t="n">
+        <v>1900</v>
+      </c>
+      <c r="B2" s="4" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="C2" s="4" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="D2" s="4" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="G2" s="4" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>39.32</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="9" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B3" s="4" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>30.83</v>
+      </c>
+      <c r="D3" s="4" t="n">
+        <v>31.19</v>
+      </c>
+      <c r="E3" s="4" t="n">
+        <v>31.19</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>33.92</v>
+      </c>
+      <c r="H3" s="4" t="n">
+        <v>34.38</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>34.86</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="n">
+        <v>2100</v>
+      </c>
+      <c r="B4" s="4" t="n">
+        <v>32.42</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>35.29</v>
+      </c>
+      <c r="D4" s="4" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="E4" s="4" t="n">
+        <v>35.65</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="G4" s="4" t="n">
+        <v>38.38</v>
+      </c>
+      <c r="H4" s="4" t="n">
+        <v>38.84</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>39.32</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>2200</v>
+      </c>
+      <c r="B5" s="4" t="n">
+        <v>30.73</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>33.6</v>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>33.96</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>33.96</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="G5" s="4" t="n">
+        <v>36.69</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>37.15</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>37.63</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>2300</v>
+      </c>
+      <c r="B6" s="4" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="C6" s="4" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D6" s="4" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="H6" s="4" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>39.43</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>2400</v>
+      </c>
+      <c r="B7" s="4" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="C7" s="4" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>39.43</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>2500</v>
+      </c>
+      <c r="B8" s="4" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D8" s="4" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="G8" s="4" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>39.43</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>2600</v>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>32.53</v>
+      </c>
+      <c r="C9" s="4" t="n">
+        <v>35.4</v>
+      </c>
+      <c r="D9" s="4" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>35.76</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>39.43</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="n">
+        <v>2700</v>
+      </c>
+      <c r="B10" s="4" t="n">
+        <v>21.44</v>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>24.31</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>24.67</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="G10" s="4" t="n">
+        <v>27.4</v>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>27.86</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>28.34</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Costo ferramenta Maico per misura (kit da regole WinPlus + voci fisse del foglio Ferramenta). Valori, non formule: rigenerare con genera_listini.py.</t>
         </is>
       </c>
     </row>
